--- a/assets/preuves/tableau-de-synthese-e5.xlsx
+++ b/assets/preuves/tableau-de-synthese-e5.xlsx
@@ -1457,7 +1457,7 @@
       <c r="A11" s="62" t="inlineStr">
         <is>
           <t>Construction de mon environnement d'apprentissage et de mon identité professionnelle
-Documents : certifications Python (IBM/Coursera, W3Schools), profils d'entraînement (TryHackMe, Root-Me), CV et profil LinkedIn.</t>
+Documents : certifications Python (IBM/Coursera, W3Schools), participation au concours de cybersécurité Passe ton Hack, CV et profil LinkedIn.</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr">
